--- a/Installation_IDs.xlsx
+++ b/Installation_IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\RStor\CEMML\ClimateChange\Document Standards\Templates\TEMPLATES_SME_Word_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD20B667-2CFD-4740-B6DB-8B2348752FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3900F204-82F0-4007-B7F0-AB0ACFBA2B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AIR FORCE" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>SITEID</t>
   </si>
@@ -34,99 +34,54 @@
     <t>SITENAME</t>
   </si>
   <si>
-    <t>FolderName</t>
-  </si>
-  <si>
     <t>Creech Air Force Base</t>
   </si>
   <si>
-    <t>Creech AFB</t>
-  </si>
-  <si>
     <t>The Barry M. Goldwater Air Force Range East (Zone 1)</t>
   </si>
   <si>
-    <t>Luke AFB</t>
-  </si>
-  <si>
     <t>Eglin Air Force Base</t>
   </si>
   <si>
-    <t>BMGR E_W</t>
-  </si>
-  <si>
     <t>Dover Air Force Base</t>
   </si>
   <si>
-    <t>Eglin</t>
-  </si>
-  <si>
     <t>Eareckson Air Force Station</t>
   </si>
   <si>
-    <t>Dover AFB</t>
-  </si>
-  <si>
     <t>Joint Base Elmendorf-Richardson</t>
   </si>
   <si>
-    <t>Eareckson AS</t>
-  </si>
-  <si>
     <t>New Boston Space Force Station</t>
   </si>
   <si>
-    <t>JB Elmendorf-Richardson</t>
-  </si>
-  <si>
     <t>45 Space Wing - Patrick Space Force Base and Cape Canaveral Air Force Base</t>
   </si>
   <si>
-    <t>New Boston SFS</t>
-  </si>
-  <si>
     <t>Edwards Air Force Base</t>
   </si>
   <si>
     <t>Eielson Air Force Base</t>
   </si>
   <si>
-    <t>Edwards</t>
-  </si>
-  <si>
     <t>Luke Air Force Base</t>
   </si>
   <si>
-    <t>Eielson AFB</t>
-  </si>
-  <si>
     <t>Joint Base McGuire-Dix-Lakehurst</t>
   </si>
   <si>
     <t>Nellis Air Force Base</t>
   </si>
   <si>
-    <t>JBMDL</t>
-  </si>
-  <si>
     <t>Joint Base Langley-Eustis - Fort Eustis</t>
   </si>
   <si>
-    <t>Nellis AFB, NTTR</t>
-  </si>
-  <si>
     <t>Joint Base Langley-Eustis - Langley Air Force Base</t>
   </si>
   <si>
-    <t>JBLE-Eustis</t>
-  </si>
-  <si>
     <t>Nevada Test and Training Range - Central</t>
   </si>
   <si>
-    <t>JBLE-Langley</t>
-  </si>
-  <si>
     <t>Nevada Test and Training Range - South</t>
   </si>
   <si>
@@ -142,9 +97,6 @@
     <t>The Barry M. Goldwater Air Force Range East (Zone 2)</t>
   </si>
   <si>
-    <t>45 Space Wing</t>
-  </si>
-  <si>
     <t>Barry Goldwater Range West</t>
   </si>
   <si>
@@ -154,82 +106,43 @@
     <t>Travis Air Force Base - Ozol Defense Fuel Support Point</t>
   </si>
   <si>
-    <t>Travis AFB</t>
-  </si>
-  <si>
     <t>Beale Air Force Base</t>
   </si>
   <si>
     <t>RAF Alconbury and RAF Molesworth</t>
   </si>
   <si>
-    <t>Beale AFB</t>
-  </si>
-  <si>
     <t>611 - King Salmon Airport</t>
   </si>
   <si>
-    <t>RAF Alconbury_Molesworth</t>
-  </si>
-  <si>
     <t>611 - Kokee Air Force Station</t>
   </si>
   <si>
-    <t>King Salmon Airport</t>
-  </si>
-  <si>
     <t>611 - Cold Bay Long Range Radar Site</t>
   </si>
   <si>
-    <t>Kokee AFS</t>
-  </si>
-  <si>
     <t>611 - Indian Mountain</t>
   </si>
   <si>
-    <t>Cold Bay LRRS</t>
-  </si>
-  <si>
     <t>611 - Fort Yukon Long Range Radar Site</t>
   </si>
   <si>
-    <t>611 Indian Mountain</t>
-  </si>
-  <si>
     <t>Wake Island Airfield</t>
   </si>
   <si>
-    <t>Fort Yukon</t>
-  </si>
-  <si>
     <t>Cannon Air Force Base and Melrose Air Force Range</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Holloman Air Force Base</t>
   </si>
   <si>
-    <t>Canon AFB</t>
-  </si>
-  <si>
     <t>MacDill Air Force Base</t>
   </si>
   <si>
-    <t>Holloman AFB</t>
-  </si>
-  <si>
     <t>Kirtland Air Force Base (Zone 1)</t>
   </si>
   <si>
-    <t>MacDill AFB</t>
-  </si>
-  <si>
     <t>Kirtland Air Force Base (Zone 2)</t>
-  </si>
-  <si>
-    <t>Kirtland AFB</t>
   </si>
   <si>
     <t>Fort Tuthill Recreation Area</t>
@@ -483,13 +396,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -776,8 +688,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="67.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" customWidth="1"/>
   </cols>
@@ -789,9 +701,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -799,10 +709,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -810,10 +717,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -821,10 +725,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -832,10 +733,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -843,10 +741,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -854,10 +749,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -865,10 +757,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -876,10 +765,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -887,7 +773,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -895,10 +781,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -906,10 +789,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -917,10 +797,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -928,10 +805,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -939,10 +813,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -950,338 +821,263 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1289,7 +1085,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1297,7 +1093,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1305,7 +1101,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1313,7 +1109,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1321,7 +1117,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1329,7 +1125,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1337,7 +1133,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1345,7 +1141,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1353,7 +1149,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1361,7 +1157,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1369,7 +1165,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1377,7 +1173,7 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1385,7 +1181,7 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -1393,7 +1189,7 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1401,7 +1197,7 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1409,7 +1205,7 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1417,7 +1213,7 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1425,7 +1221,7 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1433,7 +1229,7 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1441,7 +1237,7 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -1449,7 +1245,7 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -1457,7 +1253,7 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -1465,7 +1261,7 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -1473,7 +1269,7 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1481,7 +1277,7 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1489,7 +1285,7 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -1497,7 +1293,7 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1505,7 +1301,7 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1513,7 +1309,7 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1521,7 +1317,7 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1529,7 +1325,7 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -1537,7 +1333,7 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -1545,7 +1341,7 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -1553,7 +1349,7 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1561,7 +1357,7 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1569,7 +1365,7 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1577,7 +1373,7 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1585,7 +1381,7 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1593,7 +1389,7 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1601,7 +1397,7 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -1609,7 +1405,7 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -1617,7 +1413,7 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1625,7 +1421,7 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -1633,7 +1429,7 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1641,7 +1437,7 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1649,7 +1445,7 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1659,12 +1455,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A06A16C-6F98-439D-96DD-17D8D49F3FE1}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="41.109375" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="41.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1672,64 +1466,67 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>125</v>
+      <c r="B2" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>126</v>
+      <c r="B3" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>127</v>
+      <c r="B4" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>128</v>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>129</v>
+      <c r="B6" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>130</v>
+      <c r="B7" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Installation_IDs.xlsx
+++ b/Installation_IDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\RStor\CEMML\ClimateChange\Document Standards\Templates\TEMPLATES_SME_Word_Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C838011553\Documents\Converter Code\GIT\HTML-Converter-RScripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3900F204-82F0-4007-B7F0-AB0ACFBA2B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45148317-81BB-4636-AEEF-36A30154ACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AIR FORCE" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>SITEID</t>
   </si>
@@ -335,13 +335,37 @@
   </si>
   <si>
     <t>Naval Submarine Base Kings Bay</t>
+  </si>
+  <si>
+    <t>InstallationID</t>
+  </si>
+  <si>
+    <t>N62688</t>
+  </si>
+  <si>
+    <t>N42237</t>
+  </si>
+  <si>
+    <t>N69212</t>
+  </si>
+  <si>
+    <t>N61008</t>
+  </si>
+  <si>
+    <t>N00207</t>
+  </si>
+  <si>
+    <t>N60201</t>
+  </si>
+  <si>
+    <t>N32446-LF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +398,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -392,9 +421,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -404,9 +434,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{0CA8EF0B-0BDB-4DAF-B59A-3C1C782D2818}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{7F1440B0-8B00-42F4-9304-B99C2DA4E6E1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1455,80 +1486,106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A06A16C-6F98-439D-96DD-17D8D49F3FE1}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="41.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>